--- a/reports/一级子公司B_资产负债表_2025-07.xlsx
+++ b/reports/一级子公司B_资产负债表_2025-07.xlsx
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0</v>
+        <v>1757000</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0</v>
+        <v>1799168</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0</v>
+        <v>1876000</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0</v>
+        <v>1921024</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0</v>
+        <v>2114000</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0</v>
+        <v>2164736</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0</v>
+        <v>2828000</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0</v>
+        <v>2895872</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0</v>
+        <v>2947000</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>0</v>
+        <v>3017728</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0</v>
+        <v>3066000</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0</v>
+        <v>3139584</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>0</v>
+        <v>3661000</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>0</v>
+        <v>3748864</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="F29" s="19" t="n">
-        <v>169500000</v>
+        <v>187749000</v>
       </c>
       <c r="G29" s="19" t="n"/>
     </row>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>0</v>
+        <v>4851000</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>0</v>
+        <v>4967424</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="F55" s="19" t="n">
-        <v>438000000</v>
+        <v>442851000</v>
       </c>
       <c r="G55" s="19" t="n"/>
     </row>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="F56" s="19" t="n">
-        <v>607500000</v>
+        <v>630600000</v>
       </c>
       <c r="G56" s="19" t="n"/>
     </row>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="F60" s="16" t="n">
-        <v>0</v>
+        <v>8302000</v>
       </c>
       <c r="G60" s="16" t="n">
-        <v>0</v>
+        <v>8501248</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1">
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="F62" s="16" t="n">
-        <v>0</v>
+        <v>8540000</v>
       </c>
       <c r="G62" s="16" t="n">
-        <v>0</v>
+        <v>8744960</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="F68" s="16" t="n">
-        <v>0</v>
+        <v>9254000</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>0</v>
+        <v>9476096</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0</v>
+        <v>9373000</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>0</v>
+        <v>9597952</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="F70" s="16" t="n">
-        <v>0</v>
+        <v>9492000</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>0</v>
+        <v>9719808</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="F78" s="16" t="n">
-        <v>0</v>
+        <v>10444000</v>
       </c>
       <c r="G78" s="16" t="n">
-        <v>0</v>
+        <v>10694656</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1">
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="F79" s="16" t="n">
-        <v>0</v>
+        <v>10563000</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>0</v>
+        <v>10816512</v>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="F84" s="19" t="n">
-        <v>118000000</v>
+        <v>183968000</v>
       </c>
       <c r="G84" s="19" t="n"/>
     </row>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="F86" s="16" t="n">
-        <v>0</v>
+        <v>11396000</v>
       </c>
       <c r="G86" s="16" t="n">
-        <v>0</v>
+        <v>11669504</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1">
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="F98" s="19" t="n">
-        <v>154000000</v>
+        <v>165396000</v>
       </c>
       <c r="G98" s="19" t="n"/>
     </row>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="F99" s="19" t="n">
-        <v>272000000</v>
+        <v>349364000</v>
       </c>
       <c r="G99" s="19" t="n"/>
     </row>
@@ -6467,7 +6467,7 @@
         </is>
       </c>
       <c r="F121" s="16" t="n">
-        <v>-9500000</v>
+        <v>-63764000</v>
       </c>
       <c r="G121" s="16" t="n">
         <v>3576877</v>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="F122" s="19" t="n">
-        <v>335500000</v>
+        <v>281236000</v>
       </c>
       <c r="G122" s="19" t="n"/>
     </row>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="F124" s="19" t="n">
-        <v>335500000</v>
+        <v>281236000</v>
       </c>
       <c r="G124" s="19" t="n"/>
     </row>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F125" s="25" t="n">
-        <v>607500000</v>
+        <v>630600000</v>
       </c>
       <c r="G125" s="25" t="n"/>
     </row>
